--- a/naver-place-crawler/results_derma/서구_피부과.xlsx
+++ b/naver-place-crawler/results_derma/서구_피부과.xlsx
@@ -624,10 +624,10 @@
         <v>938</v>
       </c>
       <c r="Q2" t="n">
-        <v>2587</v>
+        <v>2588</v>
       </c>
       <c r="R2" t="n">
-        <v>3525</v>
+        <v>3526</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -849,7 +849,11 @@
           <t>디앤유비뇨기과의원</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>binterest@naver.com</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
@@ -1033,11 +1037,7 @@
           <t>블리비의원 발산점</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>gp___e@naver.com</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
@@ -1282,10 +1282,10 @@
         <v>1434</v>
       </c>
       <c r="Q9" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="R9" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1507,11 +1507,7 @@
           <t>손한나의원</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>kimdaisuke@naver.com</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
@@ -1846,10 +1842,10 @@
         <v>294</v>
       </c>
       <c r="Q15" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="R15" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2038,10 +2034,10 @@
         <v>1175</v>
       </c>
       <c r="Q17" t="n">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="R17" t="n">
-        <v>2978</v>
+        <v>2979</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2263,7 +2259,11 @@
           <t>미엘피부과의원</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>mgsj010@naver.com</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
@@ -2353,7 +2353,11 @@
           <t>유피부과의원</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0ghffhtjrl0@naver.com</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
@@ -2500,10 +2504,10 @@
         <v>2437</v>
       </c>
       <c r="Q22" t="n">
-        <v>3876</v>
+        <v>3875</v>
       </c>
       <c r="R22" t="n">
-        <v>6313</v>
+        <v>6312</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2537,7 +2541,11 @@
           <t>엘레슈의원 인천부평</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>jaerin88@naver.com</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
@@ -2909,7 +2917,11 @@
           <t>타임피부과의원</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>minime75@naver.com</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
@@ -3056,10 +3068,10 @@
         <v>541</v>
       </c>
       <c r="Q28" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="R28" t="n">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3187,11 +3199,7 @@
           <t>비아프의원</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>climate1149@naver.com</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
@@ -3338,10 +3346,10 @@
         <v>1730</v>
       </c>
       <c r="Q31" t="n">
-        <v>2685</v>
+        <v>2699</v>
       </c>
       <c r="R31" t="n">
-        <v>4415</v>
+        <v>4429</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3433,13 +3441,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="Q32" t="n">
         <v>2791</v>
       </c>
       <c r="R32" t="n">
-        <v>4095</v>
+        <v>4096</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3473,11 +3481,7 @@
           <t>연세미소의원</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>fmdr99@naver.com</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
@@ -3755,11 +3759,7 @@
           <t>이화별의원</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>kmu2333@naver.com</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
@@ -3906,10 +3906,10 @@
         <v>171</v>
       </c>
       <c r="Q37" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="R37" t="n">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -4229,11 +4229,7 @@
           <t>청라의원</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>cnvclinic@naver.com</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
@@ -4760,10 +4756,10 @@
         <v>2107</v>
       </c>
       <c r="Q46" t="n">
-        <v>4467</v>
+        <v>4464</v>
       </c>
       <c r="R46" t="n">
-        <v>6574</v>
+        <v>6571</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4854,10 +4850,10 @@
         <v>17749</v>
       </c>
       <c r="Q47" t="n">
-        <v>8761</v>
+        <v>8771</v>
       </c>
       <c r="R47" t="n">
-        <v>26510</v>
+        <v>26520</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -5042,10 +5038,10 @@
         <v>1747</v>
       </c>
       <c r="Q49" t="n">
-        <v>8735</v>
+        <v>8736</v>
       </c>
       <c r="R49" t="n">
-        <v>10482</v>
+        <v>10483</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5173,7 +5169,11 @@
           <t>다시봄날의원 가정청라점</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>springdayclinic12@naver.com</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
@@ -5263,11 +5263,7 @@
           <t>장피부과의원</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1sanginfl@naver.com</t>
-        </is>
-      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>jangskin@lycos.co.kr</t>
@@ -5418,10 +5414,10 @@
         <v>339</v>
       </c>
       <c r="Q53" t="n">
-        <v>2889</v>
+        <v>2899</v>
       </c>
       <c r="R53" t="n">
-        <v>3228</v>
+        <v>3238</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -6076,10 +6072,10 @@
         <v>2921</v>
       </c>
       <c r="Q60" t="n">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="R60" t="n">
-        <v>4006</v>
+        <v>4007</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6113,11 +6109,7 @@
           <t>미소가인피부과의원 김포점</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>misogainep@naver.com</t>
-        </is>
-      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
@@ -6358,10 +6350,10 @@
         <v>2252</v>
       </c>
       <c r="Q63" t="n">
-        <v>5251</v>
+        <v>5252</v>
       </c>
       <c r="R63" t="n">
-        <v>7503</v>
+        <v>7504</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6452,10 +6444,10 @@
         <v>161</v>
       </c>
       <c r="Q64" t="n">
-        <v>4661</v>
+        <v>4665</v>
       </c>
       <c r="R64" t="n">
-        <v>4822</v>
+        <v>4826</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6640,10 +6632,10 @@
         <v>639</v>
       </c>
       <c r="Q66" t="n">
-        <v>1609</v>
+        <v>1614</v>
       </c>
       <c r="R66" t="n">
-        <v>2248</v>
+        <v>2253</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -7021,13 +7013,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="Q70" t="n">
         <v>1227</v>
       </c>
       <c r="R70" t="n">
-        <v>2698</v>
+        <v>2699</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7061,11 +7053,7 @@
           <t>미엘피부과의원</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>mgsj010@naver.com</t>
-        </is>
-      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
@@ -7339,11 +7327,7 @@
           <t>고운의원</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>thegounclinic@naver.com</t>
-        </is>
-      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
@@ -7433,11 +7417,7 @@
           <t>뷰티온의원 인천계양점</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>mingming9706@naver.com</t>
-        </is>
-      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
@@ -7960,10 +7940,10 @@
         <v>490</v>
       </c>
       <c r="Q80" t="n">
-        <v>3500</v>
+        <v>3507</v>
       </c>
       <c r="R80" t="n">
-        <v>3990</v>
+        <v>3997</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -8336,10 +8316,10 @@
         <v>1274</v>
       </c>
       <c r="Q84" t="n">
-        <v>5988</v>
+        <v>6000</v>
       </c>
       <c r="R84" t="n">
-        <v>7262</v>
+        <v>7274</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8528,10 +8508,10 @@
         <v>1049</v>
       </c>
       <c r="Q86" t="n">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="R86" t="n">
-        <v>3457</v>
+        <v>3459</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8622,10 +8602,10 @@
         <v>1617</v>
       </c>
       <c r="Q87" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="R87" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8717,13 +8697,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>5007</v>
+        <v>5006</v>
       </c>
       <c r="Q88" t="n">
         <v>4395</v>
       </c>
       <c r="R88" t="n">
-        <v>9402</v>
+        <v>9401</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8908,10 +8888,10 @@
         <v>448</v>
       </c>
       <c r="Q90" t="n">
-        <v>5756</v>
+        <v>5770</v>
       </c>
       <c r="R90" t="n">
-        <v>6204</v>
+        <v>6218</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -9093,13 +9073,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>22832</v>
+        <v>22833</v>
       </c>
       <c r="Q92" t="n">
-        <v>6459</v>
+        <v>6460</v>
       </c>
       <c r="R92" t="n">
-        <v>29291</v>
+        <v>29293</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9281,13 +9261,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="Q94" t="n">
         <v>1140</v>
       </c>
       <c r="R94" t="n">
-        <v>3140</v>
+        <v>3141</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9566,10 +9546,10 @@
         <v>1878</v>
       </c>
       <c r="Q97" t="n">
-        <v>4165</v>
+        <v>4166</v>
       </c>
       <c r="R97" t="n">
-        <v>6043</v>
+        <v>6044</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9603,7 +9583,11 @@
           <t>블리비의원 김포점</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>lukxymxl@naver.com</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
@@ -9938,10 +9922,10 @@
         <v>3191</v>
       </c>
       <c r="Q101" t="n">
-        <v>19978</v>
+        <v>19981</v>
       </c>
       <c r="R101" t="n">
-        <v>23169</v>
+        <v>23172</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -10445,11 +10429,7 @@
           <t>오라클피부과의원 검단점</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>uoejxua113@naver.com</t>
-        </is>
-      </c>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
@@ -10915,11 +10895,7 @@
           <t>디테일러스</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>wwwss88@naver.com</t>
-        </is>
-      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
@@ -11287,7 +11263,11 @@
           <t>현대중앙의원</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>grace2138@naver.com</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
@@ -11471,11 +11451,7 @@
           <t>우충아의원</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>meschool24@naver.com</t>
-        </is>
-      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
@@ -12125,7 +12101,11 @@
           <t>엘림비뇨기과의원</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>binterest@naver.com</t>
+        </is>
+      </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
@@ -12215,7 +12195,11 @@
           <t>미소퀸의원</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>gomlovegomlove@naver.com</t>
+        </is>
+      </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
@@ -12456,10 +12440,10 @@
         <v>623</v>
       </c>
       <c r="Q128" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="R128" t="n">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -12493,7 +12477,11 @@
           <t>사랑소아청소년과의원</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>srpc0610@naver.com</t>
+        </is>
+      </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
@@ -12730,10 +12718,10 @@
         <v>1100</v>
       </c>
       <c r="Q131" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R131" t="n">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -12955,7 +12943,11 @@
           <t>강약국</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>shr0614@naver.com</t>
+        </is>
+      </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
@@ -13290,10 +13282,10 @@
         <v>437</v>
       </c>
       <c r="Q137" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="R137" t="n">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -13703,7 +13695,11 @@
           <t>이대서울병원</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>ddonu999@naver.com</t>
+        </is>
+      </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
@@ -13756,10 +13752,10 @@
         <v>1717</v>
       </c>
       <c r="Q142" t="n">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="R142" t="n">
-        <v>3485</v>
+        <v>3486</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -13850,10 +13846,10 @@
         <v>870</v>
       </c>
       <c r="Q143" t="n">
-        <v>5428</v>
+        <v>5435</v>
       </c>
       <c r="R143" t="n">
-        <v>6298</v>
+        <v>6305</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -13944,10 +13940,10 @@
         <v>919</v>
       </c>
       <c r="Q144" t="n">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="R144" t="n">
-        <v>2999</v>
+        <v>3000</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -14132,10 +14128,10 @@
         <v>1023</v>
       </c>
       <c r="Q146" t="n">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="R146" t="n">
-        <v>3227</v>
+        <v>3228</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -14508,10 +14504,10 @@
         <v>511</v>
       </c>
       <c r="Q150" t="n">
-        <v>2317</v>
+        <v>2322</v>
       </c>
       <c r="R150" t="n">
-        <v>2828</v>
+        <v>2833</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -14602,10 +14598,10 @@
         <v>996</v>
       </c>
       <c r="Q151" t="n">
-        <v>3773</v>
+        <v>3774</v>
       </c>
       <c r="R151" t="n">
-        <v>4769</v>
+        <v>4770</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_derma/서구_피부과.xlsx
+++ b/naver-place-crawler/results_derma/서구_피부과.xlsx
@@ -661,7 +661,11 @@
           <t>서울더본피부과의원</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>darguji@naver.com</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
@@ -686,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1037,7 +1041,11 @@
           <t>블리비의원 발산점</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>gp___e@naver.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
@@ -1057,12 +1065,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1078,12 +1086,12 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1507,7 +1515,11 @@
           <t>손한나의원</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>kimdaisuke@naver.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
@@ -1978,11 +1990,7 @@
           <t>detach3975@naver.com</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>mdvision@nate.com</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>031-8049-6024</t>
@@ -2022,7 +2030,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2189,7 +2197,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2471,12 +2479,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2492,12 +2500,12 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -3068,10 +3076,10 @@
         <v>541</v>
       </c>
       <c r="Q28" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="R28" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3199,7 +3207,11 @@
           <t>비아프의원</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>girl79351@naver.com</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
@@ -3346,10 +3358,10 @@
         <v>1730</v>
       </c>
       <c r="Q31" t="n">
-        <v>2699</v>
+        <v>2700</v>
       </c>
       <c r="R31" t="n">
-        <v>4429</v>
+        <v>4430</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3388,11 +3400,7 @@
           <t>hndicp79400@naver.com</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>mdvision@nate.com</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>032-716-6033</t>
@@ -3432,7 +3440,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3441,13 +3449,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="Q32" t="n">
         <v>2791</v>
       </c>
       <c r="R32" t="n">
-        <v>4096</v>
+        <v>4097</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3481,7 +3489,11 @@
           <t>연세미소의원</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>fmdr99@naver.com</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
@@ -3719,13 +3731,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3040</v>
+        <v>3041</v>
       </c>
       <c r="Q35" t="n">
         <v>2538</v>
       </c>
       <c r="R35" t="n">
-        <v>5578</v>
+        <v>5579</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3759,7 +3771,11 @@
           <t>이화별의원</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>kmu2333@naver.com</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
@@ -4070,7 +4086,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4086,7 +4102,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4189,13 +4205,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="Q40" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="R40" t="n">
-        <v>1235</v>
+        <v>1242</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4229,7 +4245,11 @@
           <t>청라의원</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>cnvclinic@naver.com</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
@@ -4606,11 +4626,7 @@
           <t>cleanup-cr@naver.com</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>promotion@cunetwork.co.kr</t>
-        </is>
-      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>0507-1421-7590</t>
@@ -4629,17 +4645,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4723,7 +4739,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4822,7 +4838,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4838,7 +4854,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -5263,7 +5279,11 @@
           <t>장피부과의원</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1sanginfl@naver.com</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>jangskin@lycos.co.kr</t>
@@ -5414,10 +5434,10 @@
         <v>339</v>
       </c>
       <c r="Q53" t="n">
-        <v>2899</v>
+        <v>2903</v>
       </c>
       <c r="R53" t="n">
-        <v>3238</v>
+        <v>3242</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5975,13 +5995,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>6403</v>
+        <v>6404</v>
       </c>
       <c r="Q59" t="n">
         <v>8471</v>
       </c>
       <c r="R59" t="n">
-        <v>14874</v>
+        <v>14875</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6072,10 +6092,10 @@
         <v>2921</v>
       </c>
       <c r="Q60" t="n">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="R60" t="n">
-        <v>4007</v>
+        <v>4008</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6109,7 +6129,11 @@
           <t>미소가인피부과의원 김포점</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>misogainep@naver.com</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
@@ -6129,12 +6153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6150,7 +6174,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6632,10 +6656,10 @@
         <v>639</v>
       </c>
       <c r="Q66" t="n">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="R66" t="n">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -7053,7 +7077,11 @@
           <t>미엘피부과의원</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>mgsj010@naver.com</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
@@ -7143,7 +7171,11 @@
           <t>더예쁨의원</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>artificial6244@naver.com</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
@@ -7327,7 +7359,11 @@
           <t>고운의원</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>thegounclinic@naver.com</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
@@ -7417,7 +7453,11 @@
           <t>뷰티온의원 인천계양점</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>mingming9706@naver.com</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
@@ -7467,13 +7507,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="Q75" t="n">
         <v>280</v>
       </c>
       <c r="R75" t="n">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7658,10 +7698,10 @@
         <v>3267</v>
       </c>
       <c r="Q77" t="n">
-        <v>4843</v>
+        <v>4844</v>
       </c>
       <c r="R77" t="n">
-        <v>8110</v>
+        <v>8111</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7818,7 +7858,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -7940,10 +7980,10 @@
         <v>490</v>
       </c>
       <c r="Q80" t="n">
-        <v>3507</v>
+        <v>3508</v>
       </c>
       <c r="R80" t="n">
-        <v>3997</v>
+        <v>3998</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -8076,7 +8116,11 @@
           <t>leehojong79@naver.com</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>barognetwork@gmail.com</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>0507-1313-5556</t>
@@ -8095,12 +8139,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -8316,10 +8360,10 @@
         <v>1274</v>
       </c>
       <c r="Q84" t="n">
-        <v>6000</v>
+        <v>6002</v>
       </c>
       <c r="R84" t="n">
-        <v>7274</v>
+        <v>7276</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8358,11 +8402,7 @@
           <t>release5554@naver.com</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>mdvision@nate.com</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>02-6949-6022</t>
@@ -8402,7 +8442,7 @@
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -8644,11 +8684,7 @@
           <t>serenity79339@naver.com</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>mdvision@nate.com</t>
-        </is>
-      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>032-721-7508</t>
@@ -8688,7 +8724,7 @@
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -8700,10 +8736,10 @@
         <v>5006</v>
       </c>
       <c r="Q88" t="n">
-        <v>4395</v>
+        <v>4401</v>
       </c>
       <c r="R88" t="n">
-        <v>9401</v>
+        <v>9407</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -9073,13 +9109,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>22833</v>
+        <v>22834</v>
       </c>
       <c r="Q92" t="n">
-        <v>6460</v>
+        <v>6461</v>
       </c>
       <c r="R92" t="n">
-        <v>29293</v>
+        <v>29295</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9137,12 +9173,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -9513,7 +9549,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9607,12 +9643,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -9628,12 +9664,12 @@
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -9795,7 +9831,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -9922,10 +9958,10 @@
         <v>3191</v>
       </c>
       <c r="Q101" t="n">
-        <v>19981</v>
+        <v>19982</v>
       </c>
       <c r="R101" t="n">
-        <v>23172</v>
+        <v>23173</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -10016,10 +10052,10 @@
         <v>981</v>
       </c>
       <c r="Q102" t="n">
-        <v>2970</v>
+        <v>2976</v>
       </c>
       <c r="R102" t="n">
-        <v>3951</v>
+        <v>3957</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -10077,17 +10113,17 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -10103,7 +10139,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P103" t="n">
@@ -10429,7 +10465,11 @@
           <t>오라클피부과의원 검단점</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>uoejxua113@naver.com</t>
+        </is>
+      </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
@@ -10895,7 +10935,11 @@
           <t>디테일러스</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>wwwss88@naver.com</t>
+        </is>
+      </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
@@ -10985,7 +11029,11 @@
           <t>하스피업</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>summer__forest@naver.com</t>
+        </is>
+      </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
@@ -11451,7 +11499,11 @@
           <t>우충아의원</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>meschool24@naver.com</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
@@ -11823,7 +11875,11 @@
           <t>365플러스의원</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>zozpok@naver.com</t>
+        </is>
+      </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
@@ -12571,7 +12627,11 @@
           <t>선소아청소년과의원</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>mintsan@naver.com</t>
+        </is>
+      </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
@@ -12755,7 +12815,11 @@
           <t>뷰티올</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>charmantyeon@naver.com</t>
+        </is>
+      </c>
       <c r="D132" t="inlineStr">
         <is>
           <t>it@beautyall.kr</t>
@@ -14001,7 +14065,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -14034,10 +14098,10 @@
         <v>1568</v>
       </c>
       <c r="Q145" t="n">
-        <v>3076</v>
+        <v>3078</v>
       </c>
       <c r="R145" t="n">
-        <v>4644</v>
+        <v>4646</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
